--- a/output/Data and Chart Outputs/ghana_energy_commission_power.xlsx
+++ b/output/Data and Chart Outputs/ghana_energy_commission_power.xlsx
@@ -25,8 +25,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="yyyy"/>
+    <numFmt numFmtId="165" formatCode="yyyy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -66,12 +66,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1293,7 +1294,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
@@ -1308,7 +1308,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
@@ -1370,7 +1369,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>36526</v>
       </c>
       <c r="B2" t="n">
@@ -1384,7 +1383,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>36892</v>
       </c>
       <c r="B3" t="n">
@@ -1398,7 +1397,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>37257</v>
       </c>
       <c r="B4" t="n">
@@ -1412,7 +1411,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>37622</v>
       </c>
       <c r="B5" t="n">
@@ -1426,7 +1425,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>37987</v>
       </c>
       <c r="B6" t="n">
@@ -1440,7 +1439,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>38353</v>
       </c>
       <c r="B7" t="n">
@@ -1454,7 +1453,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>38718</v>
       </c>
       <c r="B8" t="n">
@@ -1468,7 +1467,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>39083</v>
       </c>
       <c r="B9" t="n">
@@ -1482,7 +1481,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>39448</v>
       </c>
       <c r="B10" t="n">
@@ -1496,7 +1495,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>39814</v>
       </c>
       <c r="B11" t="n">
@@ -1510,7 +1509,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>40179</v>
       </c>
       <c r="B12" t="n">
@@ -1524,7 +1523,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>40544</v>
       </c>
       <c r="B13" t="n">
@@ -1538,7 +1537,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>40909</v>
       </c>
       <c r="B14" t="n">
@@ -1552,7 +1551,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>41275</v>
       </c>
       <c r="B15" t="n">
@@ -1566,7 +1565,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>41640</v>
       </c>
       <c r="B16" t="n">
@@ -1580,7 +1579,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>42005</v>
       </c>
       <c r="B17" t="n">
@@ -1594,7 +1593,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>42370</v>
       </c>
       <c r="B18" t="n">
@@ -1608,7 +1607,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>42736</v>
       </c>
       <c r="B19" t="n">
@@ -1622,7 +1621,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>43101</v>
       </c>
       <c r="B20" t="n">
@@ -1636,7 +1635,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>43466</v>
       </c>
       <c r="B21" t="n">
@@ -1650,7 +1649,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>43831</v>
       </c>
       <c r="B22" t="n">
@@ -1664,7 +1663,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B23" t="n">
@@ -1678,7 +1677,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B24" t="n">
@@ -1692,7 +1691,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B25" t="n">
@@ -1706,7 +1705,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B26" t="n">
@@ -1720,7 +1719,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B27" t="n">
